--- a/Result/profitability/1582.xlsx
+++ b/Result/profitability/1582.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>1.86</v>
       </c>
       <c r="M2" t="n">
-        <v>1.095</v>
+        <v>1.0675</v>
       </c>
       <c r="N2" t="n">
-        <v>23.8825</v>
+        <v>22.00625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.72</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.085</v>
       </c>
       <c r="N3" t="n">
-        <v>23.055</v>
+        <v>21.425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1475</v>
+        <v>1.17875</v>
       </c>
       <c r="N4" t="n">
-        <v>22.79875</v>
+        <v>21.2775</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.19</v>
       </c>
       <c r="M5" t="n">
-        <v>1.165</v>
+        <v>1.2225</v>
       </c>
       <c r="N5" t="n">
-        <v>21.77625</v>
+        <v>20.63625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.21</v>
       </c>
       <c r="M6" t="n">
-        <v>1.21125</v>
+        <v>1.2375</v>
       </c>
       <c r="N6" t="n">
-        <v>22.28</v>
+        <v>21.1475</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.46</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2575</v>
+        <v>1.36125</v>
       </c>
       <c r="N7" t="n">
-        <v>23.015</v>
+        <v>22.15375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.76</v>
       </c>
       <c r="M8" t="n">
-        <v>1.41875</v>
+        <v>1.5375</v>
       </c>
       <c r="N8" t="n">
-        <v>24.32</v>
+        <v>23.5975</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1582</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1722</v>
+      </c>
+      <c r="E75" t="n">
+        <v>285</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-37</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>218</v>
+      </c>
+      <c r="J75" t="n">
+        <v>181</v>
+      </c>
+      <c r="K75" t="n">
+        <v>187</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.07375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.714285714285715</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.779999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2894341512268402</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.4600000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5476190476190477</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3912483912483913</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
